--- a/data/value_of_passenger_flight.xlsx
+++ b/data/value_of_passenger_flight.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B47717-9A1C-4DAA-AF7B-3943FC9AAA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679C0106-C15A-462B-86BC-26B1F1991206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,8 +89,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,33 +394,33 @@
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>32937</v>
-      </c>
-      <c r="C2">
-        <v>6043</v>
+      <c r="B2" s="1">
+        <v>33747.220218120812</v>
+      </c>
+      <c r="C2" s="1">
+        <v>6191.5880872483231</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>989</v>
-      </c>
-      <c r="C3">
-        <v>178</v>
+      <c r="B3" s="1">
+        <v>1012.8903104026847</v>
+      </c>
+      <c r="C3" s="1">
+        <v>182.51531040268458</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>1780</v>
-      </c>
-      <c r="C4">
-        <v>881</v>
+      <c r="B4" s="1">
+        <v>1823.7598573825505</v>
+      </c>
+      <c r="C4" s="1">
+        <v>902.82382550335581</v>
       </c>
     </row>
   </sheetData>
